--- a/text_log.xlsx
+++ b/text_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,504 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0:00</t>
+          <t>0:00:08.960</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Bir  de  annem  dedik  ki  Sahir  Paşa 'lara  giderken  anneyi  sevdiyesini  hazırlasın.</t>
+          <t xml:space="preserve"> Büyümlesin  efendim,  beni  şartmışsınız.  Ha,  lala.  Çalışanlara  tembih  et  lütfen.  Hiçbir  şey  israf  etmesinler.  Zor  günlerden  geçeceğiz.  Babı  efendim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0:00:20.880</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Eee  bir  de  şey  soracaktım.  Bugün  bolstacı  geldi  mi?  Gel  de  efendim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0:00:25.820</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Bir  tattan  haber  var.  Yok.  Ama  merak  etmeyin.  Yarın  öbür  gün.  Gelir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0:00:31.460</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sağ  ol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0:00:48.020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sağ  ol.  Biliyor  musun  Aşı?  Annem  beni  evlendirdiğinde  o  beş  yaşındaydım.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0:00:56.220</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> O  yılda  hamile  kaldım.  Ha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0:01:01.250</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Daha  kendim  çocukluğum  yani.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0:01:04.840</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hamileliğim  ramağına  denk  gelmiştim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0:01:08.160</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Bir  gece  sabır  da.  Davucunun  sesini  duyunca  sokağı  fırladım.  Ben  de  göbeğimi  uğra  uğra  dolaştım.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0:01:20.680</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Reşar  da  oynamak  isterdim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0:01:24.220</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> İzin  mermezlerdi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0:01:27.700</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Artık  evlesin  çocuk  değilsin  derlerdi.  Sen  çocuk  değilsin  değilce.  Çocukluk  bitiyormuş  ki.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0:01:37.600</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ama  bir  tatdayın.  Ah  benim  bir  tamağa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0:01:43.280</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ama  bana  hiç  kıyamazdı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0:01:46.180</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Bütün  çocuklar  sokakta  oynarken.  Bu  benimle  evde  oturup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0:01:51.960</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Gizli  gizli  oyun  kul  artık.  Ah  bir  tatım  benim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0:01:58.480</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hiç  kıyamazdı  bana  hiç.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0:02:01.620</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Bazen  de  hatırımı  kırmamak  için.  Bebekler  bunlar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0:02:11.860</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Merak  etmeyin.  Bir  tatdayım  sağ  salim  dönecektir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0:02:16.760</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hem  onun  olduğu  taraflarda  hareket  yok  ki.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0:02:20.280</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> İnşallah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0:02:22.480</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Komitacının  nerede  olduğu  belli  olmuyor  ya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0:02:28.980</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Anneciğim  sahil  poşalar  haber  verdiniz  mi?  Ne  haberi?  Ev  ziyaretini  sırası  değil  tehir  edelim  demiştiniz  yani.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0:02:37.900</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tamam  tamam.  Ben  öyle  düşünüyordum  ama  bana  öyle  düşünmüyor.  Büyük  bir  ayaklama  değil  o  dedi.  Gidilecek  yani.  Evet.  Peki  o  zaman  ben  annesi  engema  haber  vereyim.  İptal  oldu  zannediyor  çünkü.  Söyle  ona.  Ne  değilsin  de  hazırlasın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0:02:59.740</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Anneciğim  kalkalım  mı?  Geç  kalıyoruz  kalkalım.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0:03:28.080</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Evet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0:03:30.960</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Evet.  Tamam  var  ya.  Geçim  emin  iyilişte  bir  yolcu  edeceğiz.  Gelecek  misınız?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0:03:36.320</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Yok  gelmeyeceğim.  Mutar  ağa  uysuz.  Hala  uyumadı.  Uyumadı  mı?  Hay  Allah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0:03:43.740</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sen  söylersin  onlara.  Ben  emin  beliye  yollacaklar  deliyorum.  Peki  söylerim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0:03:50.520</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ee  bir  de...  Annem  dedi  ki...  Sahir  Paşalara  giderken  annesi  hediyesini  hazırlesin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0:04:31.200</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Böylim  gündür  çıksın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0:04:34.220</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tek  bir  kelime  etmeden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0:04:41.360</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Babana  tekrar  söyledim.  Al  böyleyken  evin  masraflarına  katkıda  bulunmazsam  rahat  edemem  diye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0:04:49.100</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ama  yine  reddetti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0:05:00.900</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sen  bunu  annene  ver,  ben  gidince.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0:05:04.580</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Babana  söylemesin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0:05:07.420</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Her  ay  göndereceğim  bir  bu  kadar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0:05:22.040</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Siz  aşağın.  Ram  Paşa  evi  leide  gidiyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0:06:08.200</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Siz  aşağın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0:06:40.060</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Siz  aşağın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0:06:50.300</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ben  sizi  görmek  istediğimi  konuşmak  istiyorum  size.  Dün  müsait  değilim  şu  an.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0:06:57.580</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Çok  mühimse  söylesin  canım.</t>
         </is>
       </c>
     </row>
